--- a/reports/2026-03-09.xlsx
+++ b/reports/2026-03-09.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Wait Candidates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Candidates'!$A$1:$AC$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AC$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AC$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trade Candidates'!$A$1:$AD$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Enter Candidates'!$A$1:$AD$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wait Candidates'!$A$1:$AD$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-09 05:25 UTC</t>
+          <t>2026-03-09 10:09 UTC</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-09_1773033835805</t>
+          <t>2026-03-09_1773050856506</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -658,20 +658,21 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -752,70 +753,75 @@
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
+          <t>Current Price (USDT)</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
           <t>Stop Price Initial</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Risk % to Stop</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>TP10 Price</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>TP20 Price</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>RR to TP10</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>RR to TP20</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Spread %</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Depth Bid 1.0% USD</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Depth Ask 1.0% USD</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>Slippage BPS 5k</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>Slippage BPS 20k</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Market Cap USD</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>BTC Regime</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
@@ -879,50 +885,53 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01425</v>
+        <v>0.01246452305960809</v>
       </c>
       <c r="P2" t="n">
+        <v>0.01413</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.009739031995369192</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>21.86598758095279</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>0.01382726859172755</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>0.015190014123847</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>0.5</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
       <c r="V2" t="n">
-        <v>0.07010164738871077</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>25836.826685</v>
+        <v>0.070546737213401</v>
       </c>
       <c r="X2" t="n">
-        <v>26283.0977678</v>
+        <v>147348.1638112</v>
       </c>
       <c r="Y2" t="n">
-        <v>32.748297</v>
+        <v>142138.4333835</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.476135</v>
+        <v>21.93851</v>
       </c>
       <c r="AA2" t="n">
-        <v>40056219.67033015</v>
-      </c>
-      <c r="AB2" t="inlineStr">
+        <v>42.413522</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>39976581.58296147</v>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -930,12 +939,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HUMAUSDT</t>
+          <t>QUBICUSDT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Huma Finance</t>
+          <t>Qubic</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -945,7 +954,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -959,10 +968,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>79.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="I3" t="n">
-        <v>79.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -982,50 +991,53 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01795</v>
+        <v>5.01246634923047e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009780070485982974</v>
+        <v>6.613e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>33.51270592850579</v>
+        <v>4.095415025932756e-07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01717448991755964</v>
+        <v>18.29541106921351</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01963929639475187</v>
+        <v>5.470992010879327e-07</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5</v>
+        <v>5.929517672528184e-07</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0.5000000000000003</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1115448968209852</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>6041.780213399999</v>
+        <v>0.4528985507246398</v>
       </c>
       <c r="X3" t="n">
-        <v>12065.5011916</v>
+        <v>3133.6566269902</v>
       </c>
       <c r="Y3" t="n">
-        <v>23.001593</v>
+        <v>3188.8641389523</v>
       </c>
       <c r="Z3" t="n">
-        <v>99.48417000000001</v>
+        <v>97.603289</v>
       </c>
       <c r="AA3" t="n">
-        <v>51796945.25398535</v>
-      </c>
-      <c r="AB3" t="inlineStr">
+        <v>694.332774</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>89588295.24474068</v>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,12 +1045,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVXUSDT</t>
+          <t>KERNELUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Convex Finance</t>
+          <t>KernelDAO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1048,7 +1060,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1062,10 +1074,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>76.05</v>
+        <v>82.16</v>
       </c>
       <c r="I4" t="n">
-        <v>76.05</v>
+        <v>82.16</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1085,50 +1097,53 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.224</v>
+        <v>0.07563282281558716</v>
       </c>
       <c r="P4" t="n">
-        <v>1.585692452707503</v>
+        <v>0.08948</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.20264788453316</v>
+        <v>0.06057244791850357</v>
       </c>
       <c r="R4" t="n">
-        <v>2.114996897594393</v>
+        <v>19.91248552735467</v>
       </c>
       <c r="S4" t="n">
-        <v>2.29143171255669</v>
+        <v>0.08316301026412895</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4999999999999997</v>
+        <v>0.09069319771267075</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08996851102115268</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>10257.65434</v>
+        <v>0.1452595117045702</v>
       </c>
       <c r="X4" t="n">
-        <v>10857.85896</v>
+        <v>7032.178279199999</v>
       </c>
       <c r="Y4" t="n">
-        <v>22.23642</v>
+        <v>3545.5958756</v>
       </c>
       <c r="Z4" t="n">
-        <v>1516.466634</v>
+        <v>61.874405</v>
       </c>
       <c r="AA4" t="n">
-        <v>221329157.2518409</v>
-      </c>
-      <c r="AB4" t="inlineStr">
+        <v>762.277681</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>25605711.30388425</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,12 +1151,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ILVUSDT</t>
+          <t>HUMAUSDT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Illuvium</t>
+          <t>Huma Finance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1151,7 +1166,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1165,19 +1180,15 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>75.29000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>75.29000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>none</t>
@@ -1192,50 +1203,53 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.793</v>
+        <v>0.01470968344036742</v>
       </c>
       <c r="P5" t="n">
-        <v>3.13912712196476</v>
+        <v>0.01774</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.83780408855047</v>
+        <v>0.009780070485982974</v>
       </c>
       <c r="R5" t="n">
-        <v>4.025217601692303</v>
+        <v>33.51270592850579</v>
       </c>
       <c r="S5" t="n">
-        <v>4.320581094934817</v>
+        <v>0.01717448991755964</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4999999999999996</v>
+        <v>0.01963929639475187</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3698811096433234</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>5288.5142728</v>
+        <v>0.1690617075232586</v>
       </c>
       <c r="X5" t="n">
-        <v>4220.921426</v>
+        <v>5145.7005397</v>
       </c>
       <c r="Y5" t="n">
-        <v>68.78542899999999</v>
+        <v>8217.850013499999</v>
       </c>
       <c r="Z5" t="n">
-        <v>2168.856</v>
+        <v>32.040839</v>
       </c>
       <c r="AA5" t="n">
-        <v>25688266.24044506</v>
-      </c>
-      <c r="AB5" t="inlineStr">
+        <v>899.628946</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>51617805.70461933</v>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,12 +1257,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KERNELUSDT</t>
+          <t>CVXUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KernelDAO</t>
+          <t>Convex Finance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1272,10 +1286,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>70.06999999999999</v>
+        <v>76.05</v>
       </c>
       <c r="I6" t="n">
-        <v>70.06999999999999</v>
+        <v>76.05</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1295,50 +1309,53 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08701</v>
+        <v>1.938562082632097</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06057244791850357</v>
+        <v>2.313</v>
       </c>
       <c r="Q6" t="n">
-        <v>19.91248552735467</v>
+        <v>1.585692452707503</v>
       </c>
       <c r="R6" t="n">
-        <v>0.08316301026412895</v>
+        <v>18.20264788453316</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09069319771267075</v>
+        <v>2.114996897594393</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5</v>
+        <v>2.29143171255669</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0.4999999999999997</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1494510547795656</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>6781.3657978</v>
+        <v>0.08643042350906568</v>
       </c>
       <c r="X6" t="n">
-        <v>6049.1955007</v>
+        <v>8302.74251</v>
       </c>
       <c r="Y6" t="n">
-        <v>52.954426</v>
+        <v>4235.24316</v>
       </c>
       <c r="Z6" t="n">
-        <v>398.290218</v>
+        <v>73.51980500000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>25193342.09170528</v>
-      </c>
-      <c r="AB6" t="inlineStr">
+        <v>3265.989538</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>231908551.5895842</v>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,12 +1363,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLUMEUSDT</t>
+          <t>COWUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plume</t>
+          <t>CoW Protocol</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1361,29 +1378,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | rebound_not_confirmed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70</v>
+        <v>70.27</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>70.27</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>rebound_not_confirmed</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>none</t>
@@ -1398,50 +1419,53 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.013103</v>
+        <v>0.2279290283946998</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008103568598526879</v>
+        <v>0.2323</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.44119846516359</v>
+        <v>0.2128215674257627</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01182536196491795</v>
+        <v>6.628142573738294</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01306595975371497</v>
+        <v>0.2354827588791684</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5</v>
+        <v>0.2430364893636369</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0.4999999999999991</v>
       </c>
       <c r="V7" t="n">
-        <v>0.09921013469684327</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>49916.26151975</v>
+        <v>0.04302000430200763</v>
       </c>
       <c r="X7" t="n">
-        <v>15495.03203907</v>
+        <v>13358.166783</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.09901</v>
+        <v>5482.028729</v>
       </c>
       <c r="Z7" t="n">
-        <v>63.800276</v>
+        <v>33.925895</v>
       </c>
       <c r="AA7" t="n">
-        <v>67002877.88105942</v>
-      </c>
-      <c r="AB7" t="inlineStr">
+        <v>1592.991942</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>129846768.892437</v>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,12 +1473,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RSRUSDT</t>
+          <t>PLUMEUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reserve Rights</t>
+          <t>Plume</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1464,7 +1488,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1478,19 +1502,15 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>68.88</v>
+        <v>70</v>
       </c>
       <c r="I8" t="n">
-        <v>68.88</v>
+        <v>70</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>none</t>
@@ -1505,50 +1525,53 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001645</v>
+        <v>0.01058476417612092</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001305520963919779</v>
+        <v>0.013352</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.76295248165533</v>
+        <v>0.008103568598526879</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001699895581973759</v>
+        <v>23.44119846516359</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001831353787991752</v>
+        <v>0.01182536196491795</v>
       </c>
       <c r="T8" t="n">
+        <v>0.01306595975371497</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.5</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
       <c r="V8" t="n">
-        <v>0.1218769043266331</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>18227.94090296</v>
+        <v>0.06738796750402702</v>
       </c>
       <c r="X8" t="n">
-        <v>15863.32870087</v>
+        <v>27907.34609868</v>
       </c>
       <c r="Y8" t="n">
-        <v>27.914942</v>
+        <v>30098.1706822</v>
       </c>
       <c r="Z8" t="n">
-        <v>71.14512999999999</v>
+        <v>3.821908</v>
       </c>
       <c r="AA8" t="n">
-        <v>102910020.9146113</v>
-      </c>
-      <c r="AB8" t="inlineStr">
+        <v>8.615515</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>68270262.39405571</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,12 +1579,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEXEUSDT</t>
+          <t>ILVUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DeXe</t>
+          <t>Illuvium</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1571,29 +1594,33 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>68</v>
+        <v>69.17</v>
       </c>
       <c r="I9" t="n">
-        <v>68</v>
+        <v>69.17</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>none</t>
@@ -1608,50 +1635,53 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.456</v>
+        <v>3.729854108449789</v>
       </c>
       <c r="P9" t="n">
-        <v>3.501886110818</v>
+        <v>3.785</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.235688885771909</v>
+        <v>3.13912712196476</v>
       </c>
       <c r="R9" t="n">
-        <v>3.911610897865954</v>
+        <v>15.83780408855047</v>
       </c>
       <c r="S9" t="n">
-        <v>4.048185826881938</v>
+        <v>4.025217601692303</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5</v>
+        <v>4.320581094934817</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1796541657309681</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>5840.8481</v>
+        <v>0.3426914458942902</v>
       </c>
       <c r="X9" t="n">
-        <v>6275.85519</v>
+        <v>4074.0187962</v>
       </c>
       <c r="Y9" t="n">
-        <v>31.850822</v>
+        <v>949.9930397999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>3517.422947</v>
+        <v>111.308867</v>
       </c>
       <c r="AA9" t="n">
-        <v>374184640.8259505</v>
-      </c>
-      <c r="AB9" t="inlineStr">
+        <v>423.933654</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>25772878.80369879</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIGNUSDT</t>
+          <t>RSRUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sign</t>
+          <t>Reserve Rights</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1674,29 +1704,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>68</v>
+        <v>68.88</v>
       </c>
       <c r="I10" t="n">
-        <v>68</v>
+        <v>68.88</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>none</t>
@@ -1711,50 +1745,53 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05527</v>
+        <v>0.001568437375955765</v>
       </c>
       <c r="P10" t="n">
-        <v>0.03853530764957305</v>
+        <v>0.001652</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.05673936750667</v>
+        <v>0.001305520963919779</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0521440499077853</v>
+        <v>16.76295248165533</v>
       </c>
       <c r="S10" t="n">
-        <v>0.05668029732718938</v>
+        <v>0.001699895581973759</v>
       </c>
       <c r="T10" t="n">
+        <v>0.001831353787991752</v>
+      </c>
+      <c r="U10" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
       <c r="V10" t="n">
-        <v>0.01807174482696858</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>9099.369103999999</v>
+        <v>0.1817631020902735</v>
       </c>
       <c r="X10" t="n">
-        <v>10404.3836038</v>
+        <v>17109.27153464</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.68588</v>
+        <v>13966.37716199</v>
       </c>
       <c r="Z10" t="n">
-        <v>123.144403</v>
+        <v>37.797885</v>
       </c>
       <c r="AA10" t="n">
-        <v>89928356.97249418</v>
-      </c>
-      <c r="AB10" t="inlineStr">
+        <v>99.99193</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>103184412.6704939</v>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,12 +1799,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIUSDT</t>
+          <t>DEXEUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pi</t>
+          <t>DeXe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1777,7 +1814,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1791,10 +1828,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="I11" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1814,50 +1851,53 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.21825</v>
+        <v>3.85884206707402</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1854072141027929</v>
+        <v>4.405</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.15403165540636</v>
+        <v>3.535631494992079</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2203222131811236</v>
+        <v>8.375843490454557</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2319605462072338</v>
+        <v>4.020447353114991</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5</v>
+        <v>4.182052639155962</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0.5000000000000013</v>
       </c>
       <c r="V11" t="n">
-        <v>0.08709403864224782</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>10665.5176627</v>
+        <v>0.1134172621072903</v>
       </c>
       <c r="X11" t="n">
-        <v>9222.897300099999</v>
+        <v>3889.27666</v>
       </c>
       <c r="Y11" t="n">
-        <v>41.568193</v>
+        <v>4401.05975</v>
       </c>
       <c r="Z11" t="n">
-        <v>117.562135</v>
+        <v>41.038143</v>
       </c>
       <c r="AA11" t="n">
-        <v>2101829671.179828</v>
-      </c>
-      <c r="AB11" t="inlineStr">
+        <v>5192.74284</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>369490712.4356059</v>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1880,7 +1920,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1894,10 +1934,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="I12" t="n">
-        <v>64.8</v>
+        <v>68</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -1917,50 +1957,53 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.10355</v>
+        <v>0.08944837061334505</v>
       </c>
       <c r="P12" t="n">
-        <v>0.07088388493647041</v>
+        <v>0.11752</v>
       </c>
       <c r="Q12" t="n">
-        <v>18.36503918251464</v>
+        <v>0.07291669345891591</v>
       </c>
       <c r="R12" t="n">
-        <v>0.09480351406162416</v>
+        <v>18.48180916105222</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1027767237700087</v>
+        <v>0.09771420919055963</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5</v>
+        <v>0.1059800477677742</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1352265043948626</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>17993.5521946</v>
+        <v>0.1103987091843159</v>
       </c>
       <c r="X12" t="n">
-        <v>15402.6243497</v>
+        <v>17407.2757029</v>
       </c>
       <c r="Y12" t="n">
-        <v>16.955427</v>
+        <v>21542.3117087</v>
       </c>
       <c r="Z12" t="n">
-        <v>59.209142</v>
+        <v>10.389949</v>
       </c>
       <c r="AA12" t="n">
-        <v>38413775.30043281</v>
-      </c>
-      <c r="AB12" t="inlineStr">
+        <v>34.217745</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>43947335.76357344</v>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,12 +2011,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHZUSDT</t>
+          <t>ZROUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chiliz</t>
+          <t>LayerZero</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1983,7 +2026,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>risk_reward_unattractive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1997,77 +2040,76 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>63.13</v>
+        <v>62.95</v>
       </c>
       <c r="I13" t="n">
-        <v>63.13</v>
+        <v>62.95</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N13" t="b">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.03794</v>
+        <v>1.790013793265306</v>
       </c>
       <c r="P13" t="n">
-        <v>0.03071231565488235</v>
+        <v>1.963</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.09580008502116</v>
+        <v>1.422371981301922</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03954988207164049</v>
+        <v>20.53849044887746</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0424957375438932</v>
+        <v>1.973834699246998</v>
       </c>
       <c r="T13" t="n">
+        <v>2.15765560522869</v>
+      </c>
+      <c r="U13" t="n">
         <v>0.5</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
       <c r="V13" t="n">
-        <v>0.02640264026401616</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>21241.9515098</v>
+        <v>0.05092946269416296</v>
       </c>
       <c r="X13" t="n">
-        <v>29652.3019395</v>
+        <v>324003.7929</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.260233</v>
+        <v>238629.39434</v>
       </c>
       <c r="Z13" t="n">
-        <v>24.893479</v>
+        <v>10.107539</v>
       </c>
       <c r="AA13" t="n">
-        <v>392430273.6686849</v>
-      </c>
-      <c r="AB13" t="inlineStr">
+        <v>24.169864</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>597956481.8979802</v>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2075,12 +2117,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZROUSDT</t>
+          <t>BANANAS31USDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LayerZero</t>
+          <t>Banana For Scale</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2090,24 +2132,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>62.95</v>
+        <v>61.6</v>
       </c>
       <c r="I14" t="n">
-        <v>62.95</v>
+        <v>61.6</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -2115,62 +2157,65 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N14" t="b">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.972</v>
+        <v>0.006617524300296796</v>
       </c>
       <c r="P14" t="n">
-        <v>1.422371981301922</v>
+        <v>0.007306</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.53849044887746</v>
+        <v>0.005399469535433958</v>
       </c>
       <c r="R14" t="n">
-        <v>1.973834699246998</v>
+        <v>18.40650233514379</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15765560522869</v>
+        <v>0.007226551682728215</v>
       </c>
       <c r="T14" t="n">
+        <v>0.007835579065159633</v>
+      </c>
+      <c r="U14" t="n">
         <v>0.5</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
       <c r="V14" t="n">
-        <v>0.05077430820004519</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>468965.07614</v>
+        <v>0.06988072319697554</v>
       </c>
       <c r="X14" t="n">
-        <v>312181.07989</v>
+        <v>8351.007220488</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.771319999999999</v>
+        <v>15899.76946221</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.954294</v>
+        <v>17.82942</v>
       </c>
       <c r="AA14" t="n">
-        <v>596054811.6574935</v>
-      </c>
-      <c r="AB14" t="inlineStr">
+        <v>78.370447</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>73365251.83459555</v>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,12 +2223,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UAIUSDT</t>
+          <t>PIUSDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UnifAI Network</t>
+          <t>Pi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2230,50 +2275,53 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3153</v>
+        <v>0.2094320820739941</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2459486444492793</v>
+        <v>0.21311</v>
       </c>
       <c r="Q15" t="n">
-        <v>22.90232624686324</v>
+        <v>0.186965178650924</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3555394236702021</v>
+        <v>10.72753667947224</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3920696834105097</v>
+        <v>0.2206655337855292</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4999999999999998</v>
+        <v>0.2318989854970643</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9999999999999997</v>
+        <v>0.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4410838059231293</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>7083.102669</v>
+        <v>0.02815051140095923</v>
       </c>
       <c r="X15" t="n">
-        <v>7974.548616</v>
+        <v>9260.3318703</v>
       </c>
       <c r="Y15" t="n">
-        <v>48.85984</v>
+        <v>12260.4153434</v>
       </c>
       <c r="Z15" t="n">
-        <v>957.806212</v>
+        <v>19.412163</v>
       </c>
       <c r="AA15" t="n">
-        <v>75139835.16934428</v>
-      </c>
-      <c r="AB15" t="inlineStr">
+        <v>99.574702</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2060834693.607751</v>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2281,12 +2329,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BANANAS31USDT</t>
+          <t>HSKUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Banana For Scale</t>
+          <t>HashKey Platform Token</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2296,29 +2344,33 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
       <c r="I16" t="n">
-        <v>60</v>
+        <v>60.4</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>none</t>
@@ -2333,50 +2385,57 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.006941</v>
+        <v>0.1636526104988297</v>
       </c>
       <c r="P16" t="n">
-        <v>0.00533702989792838</v>
+        <v>0.1728</v>
       </c>
       <c r="Q16" t="n">
-        <v>18.80180028026063</v>
+        <v>0.1424215424015932</v>
       </c>
       <c r="R16" t="n">
-        <v>0.007190749018124003</v>
+        <v>12.97325354757376</v>
       </c>
       <c r="S16" t="n">
-        <v>0.007808655391522544</v>
+        <v>0.1742681445474479</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5</v>
+        <v>0.1848836785960662</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0.4999999999999993</v>
       </c>
       <c r="V16" t="n">
-        <v>0.03165376535926944</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>13031.793321126</v>
+        <v>0.1735608909459038</v>
       </c>
       <c r="X16" t="n">
-        <v>17457.306752148</v>
+        <v>3743.269667</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.706187</v>
+        <v>18482.218747</v>
       </c>
       <c r="Z16" t="n">
-        <v>68.730102</v>
+        <v>37.944413</v>
       </c>
       <c r="AA16" t="n">
-        <v>68989854.5765613</v>
-      </c>
-      <c r="AB16" t="inlineStr">
+        <v>72.01785700000001</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>59628929.72306599</v>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,12 +2443,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OKBUSDT</t>
+          <t>TRXUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OKB</t>
+          <t>TRON</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2399,7 +2458,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>risk_reward_unattractive</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2413,10 +2472,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>59.44</v>
+        <v>60.34</v>
       </c>
       <c r="I17" t="n">
-        <v>59.44</v>
+        <v>60.34</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -2424,62 +2483,65 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N17" t="b">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>98.56699999999999</v>
+        <v>0.284693334781343</v>
       </c>
       <c r="P17" t="n">
-        <v>69.07337904094946</v>
+        <v>0.2877</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.47336866758937</v>
+        <v>0.2748952457319503</v>
       </c>
       <c r="R17" t="n">
-        <v>92.5507012720777</v>
+        <v>3.441629238323416</v>
       </c>
       <c r="S17" t="n">
-        <v>100.3764753491204</v>
+        <v>0.2895923793060393</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5000000000000004</v>
+        <v>0.2944914238307356</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0.4999999999999972</v>
       </c>
       <c r="V17" t="n">
-        <v>0.06184762165477147</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>26482.772962</v>
+        <v>0.03475238922675551</v>
       </c>
       <c r="X17" t="n">
-        <v>35258.185823</v>
+        <v>4169159.423793</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.499411</v>
+        <v>4533510.05926</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.573728</v>
+        <v>4.826294</v>
       </c>
       <c r="AA17" t="n">
-        <v>2073391477.983172</v>
-      </c>
-      <c r="AB17" t="inlineStr">
+        <v>7.418167</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>27250132528.113</v>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2487,12 +2549,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GMXUSDT</t>
+          <t>SIGNUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GMX</t>
+          <t>Sign</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2502,33 +2564,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>tradeability_marginal | risk_reward_unattractive</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="I18" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>none</t>
@@ -2543,50 +2601,53 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>6.094</v>
+        <v>0.04827182128793071</v>
       </c>
       <c r="P18" t="n">
-        <v>5.750401195585613</v>
+        <v>0.05498</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.55250039850605</v>
+        <v>0.03950021971180025</v>
       </c>
       <c r="R18" t="n">
-        <v>7.2194210512971</v>
+        <v>18.17126709143581</v>
       </c>
       <c r="S18" t="n">
-        <v>7.709094336534261</v>
+        <v>0.05265762207599594</v>
       </c>
       <c r="T18" t="n">
+        <v>0.05704342286406117</v>
+      </c>
+      <c r="U18" t="n">
         <v>0.5000000000000004</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
       <c r="V18" t="n">
-        <v>0.1477226097661115</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>5157.522980000001</v>
+        <v>0.0363372093023241</v>
       </c>
       <c r="X18" t="n">
-        <v>2596.95258</v>
+        <v>8943.840643199999</v>
       </c>
       <c r="Y18" t="n">
-        <v>138.716004</v>
+        <v>10277.3964194</v>
       </c>
       <c r="Z18" t="n">
-        <v>4196.912951</v>
+        <v>14.614396</v>
       </c>
       <c r="AA18" t="n">
-        <v>62989711.07064917</v>
-      </c>
-      <c r="AB18" t="inlineStr">
+        <v>159.15585</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>90281927.47045857</v>
+      </c>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2594,12 +2655,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KAVAUSDT</t>
+          <t>UAIUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kava</t>
+          <t>UnifAI Network</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2614,19 +2675,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>58.6</v>
+        <v>60</v>
       </c>
       <c r="I19" t="n">
-        <v>58.6</v>
+        <v>60</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2646,50 +2707,53 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06390999999999999</v>
+        <v>0.3170273387954089</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0446773128928048</v>
+        <v>0.2463</v>
       </c>
       <c r="Q19" t="n">
-        <v>21.52493913278071</v>
+        <v>0.2440425695288501</v>
       </c>
       <c r="R19" t="n">
-        <v>0.06305913566566616</v>
+        <v>23.02160108458627</v>
       </c>
       <c r="S19" t="n">
-        <v>0.06918640992328662</v>
+        <v>0.3535197234286883</v>
       </c>
       <c r="T19" t="n">
+        <v>0.3900121080619677</v>
+      </c>
+      <c r="U19" t="n">
         <v>0.5</v>
       </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
       <c r="V19" t="n">
-        <v>0.1095718869844261</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>3980.6456428</v>
+        <v>0.2858893199918342</v>
       </c>
       <c r="X19" t="n">
-        <v>5708.4124177</v>
+        <v>3285.326182</v>
       </c>
       <c r="Y19" t="n">
-        <v>32.195171</v>
+        <v>6808.463448</v>
       </c>
       <c r="Z19" t="n">
-        <v>6071.338793</v>
+        <v>60.759115</v>
       </c>
       <c r="AA19" t="n">
-        <v>68967364.57295211</v>
-      </c>
-      <c r="AB19" t="inlineStr">
+        <v>226.252923</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>59078928.7593796</v>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2697,12 +2761,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LUNAUSDT</t>
+          <t>OKBUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Terra</t>
+          <t>OKB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2712,7 +2776,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>tradeability_marginal | risk_reward_unattractive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2726,19 +2790,15 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>57.31</v>
+        <v>59.44</v>
       </c>
       <c r="I20" t="n">
-        <v>57.31</v>
+        <v>59.44</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>none</t>
@@ -2753,50 +2813,53 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.06320000000000001</v>
+        <v>84.72492719503495</v>
       </c>
       <c r="P20" t="n">
-        <v>0.05368674026100174</v>
+        <v>97.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.10471445579958</v>
+        <v>69.07337904094946</v>
       </c>
       <c r="R20" t="n">
-        <v>0.06914546865719852</v>
+        <v>18.47336866758937</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07429837812259744</v>
+        <v>92.5507012720777</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5</v>
+        <v>100.3764753491204</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1424163304058972</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>5304.8596996</v>
+        <v>0.04700592683424511</v>
       </c>
       <c r="X20" t="n">
-        <v>5542.7371414</v>
+        <v>31148.609453</v>
       </c>
       <c r="Y20" t="n">
-        <v>60.97981</v>
+        <v>34471.371002</v>
       </c>
       <c r="Z20" t="n">
-        <v>172.875353</v>
+        <v>15.30352</v>
       </c>
       <c r="AA20" t="n">
-        <v>44818352.36579417</v>
-      </c>
-      <c r="AB20" t="inlineStr">
+        <v>23.385367</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2052888180.884619</v>
+      </c>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2804,12 +2867,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KITEUSDT</t>
+          <t>GMXUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kite</t>
+          <t>GMX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2819,29 +2882,33 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>56.8</v>
+        <v>58.95</v>
       </c>
       <c r="I21" t="n">
-        <v>56.8</v>
+        <v>58.95</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>none</t>
@@ -2856,53 +2923,56 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.29132</v>
+        <v>6.729747766059937</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2412191557968445</v>
+        <v>6.376</v>
       </c>
       <c r="Q21" t="n">
-        <v>13.8424842936496</v>
+        <v>5.750401195585613</v>
       </c>
       <c r="R21" t="n">
-        <v>0.299352314838229</v>
+        <v>14.55250039850605</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3187300345186905</v>
+        <v>7.2194210512971</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4999999999999993</v>
+        <v>7.709094336534261</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0.5000000000000004</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0516786963187485</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>10529.3252143</v>
+        <v>0.1254705144291093</v>
       </c>
       <c r="X21" t="n">
-        <v>7279.8484574</v>
+        <v>4595.482660000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.082944</v>
+        <v>2690.02586</v>
       </c>
       <c r="Z21" t="n">
-        <v>339.164865</v>
+        <v>95.551092</v>
       </c>
       <c r="AA21" t="n">
-        <v>523977502.3544809</v>
-      </c>
-      <c r="AB21" t="inlineStr">
+        <v>1534.868484</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>66221289.71012631</v>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC21"/>
+  <autoFilter ref="A1:AD21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2913,7 +2983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2931,20 +3001,21 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3025,77 +3096,82 @@
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
+          <t>Current Price (USDT)</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
           <t>Stop Price Initial</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Risk % to Stop</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>TP10 Price</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>TP20 Price</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>RR to TP10</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>RR to TP20</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Spread %</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Depth Bid 1.0% USD</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Depth Ask 1.0% USD</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>Slippage BPS 5k</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>Slippage BPS 20k</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Market Cap USD</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>BTC Regime</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC1"/>
+  <autoFilter ref="A1:AD1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3106,7 +3182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3124,20 +3200,21 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3218,77 +3295,82 @@
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
+          <t>Current Price (USDT)</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
           <t>Stop Price Initial</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Risk % to Stop</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>TP10 Price</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>TP20 Price</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>RR to TP10</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>RR to TP20</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Spread %</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Depth Bid 1.0% USD</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Depth Ask 1.0% USD</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>Slippage BPS 5k</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>Slippage BPS 20k</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Market Cap USD</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>BTC Regime</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Flags</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC1"/>
+  <autoFilter ref="A1:AD1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/2026-03-09.xlsx
+++ b/reports/2026-03-09.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-09 15:01 UTC</t>
+          <t>2026-03-09 17:38 UTC</t>
         </is>
       </c>
     </row>
@@ -587,43 +587,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>run_id</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-09_1773068369979</t>
-        </is>
+          <t>entry_state_counts_all.early</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>canonical_schema_version</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5.7.0</t>
-        </is>
+          <t>entry_state_counts_all.at_trigger</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Total Symbols Scanned</t>
-        </is>
+          <t>entry_state_counts_all.late</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Symbols Filtered (MidCaps)</t>
-        </is>
+          <t>entry_state_counts_all.chased</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>entry_state_counts_all.null</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run_id</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-09_1773077824298</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>canonical_schema_version</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5.7.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Symbols Scanned</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Symbols Filtered (MidCaps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Symbols in Shortlist</t>
         </is>
@@ -860,7 +910,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -900,10 +950,10 @@
         <v>0.01246452305960809</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01416</v>
+        <v>0.01442</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.60242130632485</v>
+        <v>15.68834147155398</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -929,22 +979,22 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07059654076949941</v>
+        <v>0.06918021445867401</v>
       </c>
       <c r="Z2" t="n">
-        <v>24115.0559265</v>
+        <v>30085.9465893</v>
       </c>
       <c r="AA2" t="n">
-        <v>16631.7867992</v>
+        <v>3015.146555</v>
       </c>
       <c r="AB2" t="n">
-        <v>29.960019</v>
+        <v>86.557845</v>
       </c>
       <c r="AC2" t="n">
-        <v>61.225339</v>
+        <v>3254.744311</v>
       </c>
       <c r="AD2" t="n">
-        <v>40348022.55925802</v>
+        <v>40982812.91584502</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -974,7 +1024,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1014,10 +1064,10 @@
         <v>5.01246634923047e-07</v>
       </c>
       <c r="P3" t="n">
-        <v>6.921e-07</v>
+        <v>6.677e-07</v>
       </c>
       <c r="Q3" t="n">
-        <v>38.07573992117741</v>
+        <v>33.20787681746879</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1043,22 +1093,22 @@
         <v>1.000000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02888920988011195</v>
+        <v>0.1496557916791492</v>
       </c>
       <c r="Z3" t="n">
-        <v>13415.403630373</v>
+        <v>3461.5358335519</v>
       </c>
       <c r="AA3" t="n">
-        <v>2826.8735842222</v>
+        <v>5537.7247560994</v>
       </c>
       <c r="AB3" t="n">
-        <v>66.191643</v>
+        <v>64.57824100000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>240.968491</v>
+        <v>415.900255</v>
       </c>
       <c r="AD3" t="n">
-        <v>95469645.37238626</v>
+        <v>91267843.1414957</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -1073,12 +1123,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NAORISUSDT</t>
+          <t>KERNELUSDT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Naoris Protocol</t>
+          <t>KernelDAO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1088,7 +1138,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1102,10 +1152,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>87.41</v>
+        <v>82.16</v>
       </c>
       <c r="I4" t="n">
-        <v>87.41</v>
+        <v>82.16</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1125,13 +1175,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03261586999869488</v>
+        <v>0.07563282281558716</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04336</v>
+        <v>0.09397</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.94141778752198</v>
+        <v>24.2449990649215</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1139,40 +1189,40 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.0189675323345019</v>
+        <v>0.06057244791850357</v>
       </c>
       <c r="T4" t="n">
-        <v>41.84569556090061</v>
+        <v>19.91248552735467</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03944003883079137</v>
+        <v>0.08316301026412895</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04626420766288786</v>
+        <v>0.09069319771267075</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1613089065560563</v>
+        <v>0.1277411113476635</v>
       </c>
       <c r="Z4" t="n">
-        <v>5220.792466800001</v>
+        <v>7178.316387</v>
       </c>
       <c r="AA4" t="n">
-        <v>5667.9482269</v>
+        <v>3846.6194129</v>
       </c>
       <c r="AB4" t="n">
-        <v>46.558275</v>
+        <v>55.302988</v>
       </c>
       <c r="AC4" t="n">
-        <v>900.991586</v>
+        <v>325.603914</v>
       </c>
       <c r="AD4" t="n">
-        <v>26093918.80592691</v>
+        <v>26932222.35667761</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1202,7 +1252,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_late</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1242,14 +1292,14 @@
         <v>0.01470968344036742</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0165</v>
+        <v>0.01508</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.17100671738087</v>
+        <v>2.517501896854757</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -1271,22 +1321,22 @@
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1212121212121163</v>
+        <v>0.133067198935457</v>
       </c>
       <c r="Z5" t="n">
-        <v>2794.6197594</v>
+        <v>8481.5830446</v>
       </c>
       <c r="AA5" t="n">
-        <v>896.0971896</v>
+        <v>2792.4836079</v>
       </c>
       <c r="AB5" t="n">
-        <v>300.298302</v>
+        <v>92.872592</v>
       </c>
       <c r="AC5" t="n">
-        <v>9302.347097</v>
+        <v>1226.110551</v>
       </c>
       <c r="AD5" t="n">
-        <v>47669566.06104178</v>
+        <v>43914591.38371933</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1301,12 +1351,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVXUSDT</t>
+          <t>ETHFIUSDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Convex Finance</t>
+          <t>ether.fi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1316,7 +1366,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1330,15 +1380,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>76.05</v>
+        <v>79.42</v>
       </c>
       <c r="I6" t="n">
-        <v>76.05</v>
+        <v>79.42</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>none</t>
@@ -1353,13 +1407,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.938562082632097</v>
+        <v>0.5082952974746983</v>
       </c>
       <c r="P6" t="n">
-        <v>2.328</v>
+        <v>0.5551</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.08900931556141</v>
+        <v>9.208171462107927</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1367,40 +1421,40 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1.585692452707503</v>
+        <v>0.4327221119461039</v>
       </c>
       <c r="T6" t="n">
-        <v>18.20264788453316</v>
+        <v>14.86796865996114</v>
       </c>
       <c r="U6" t="n">
-        <v>2.114996897594393</v>
+        <v>0.5460818902389954</v>
       </c>
       <c r="V6" t="n">
-        <v>2.29143171255669</v>
+        <v>0.5838684830032926</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4999999999999997</v>
+        <v>0.5</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.08583690987123517</v>
+        <v>0.09009820704568985</v>
       </c>
       <c r="Z6" t="n">
-        <v>10508.70111</v>
+        <v>185432.781518</v>
       </c>
       <c r="AA6" t="n">
-        <v>6660.52185</v>
+        <v>196281.014515</v>
       </c>
       <c r="AB6" t="n">
-        <v>39.982519</v>
+        <v>13.158013</v>
       </c>
       <c r="AC6" t="n">
-        <v>2533.220694</v>
+        <v>17.757193</v>
       </c>
       <c r="AD6" t="n">
-        <v>233065258.2278105</v>
+        <v>413377676.4828406</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1415,12 +1469,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PLUMEUSDT</t>
+          <t>HYPEUSDT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plume</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1430,7 +1484,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1444,10 +1498,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>70</v>
+        <v>77.97</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>77.97</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1467,13 +1521,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01058476417612092</v>
+        <v>30.28971634021515</v>
       </c>
       <c r="P7" t="n">
-        <v>0.013246</v>
+        <v>33.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.14213618365526</v>
+        <v>11.85314388374805</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1481,40 +1535,40 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0.008103568598526879</v>
+        <v>25.43437556795867</v>
       </c>
       <c r="T7" t="n">
-        <v>23.44119846516359</v>
+        <v>16.02966735548504</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01182536196491795</v>
+        <v>32.7173867263434</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01306595975371497</v>
+        <v>35.14505711247164</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000003</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.120909846595622</v>
+        <v>0.02951158329643798</v>
       </c>
       <c r="Z7" t="n">
-        <v>15362.22924076</v>
+        <v>38760.1116</v>
       </c>
       <c r="AA7" t="n">
-        <v>5034.02297959</v>
+        <v>65413.2671</v>
       </c>
       <c r="AB7" t="n">
-        <v>47.44714</v>
+        <v>8.848145000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>137.417678</v>
+        <v>14.153559</v>
       </c>
       <c r="AD7" t="n">
-        <v>68101025.2879142</v>
+        <v>8755867548.296934</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1529,12 +1583,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARIAUSDT</t>
+          <t>CVXUSDT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AriaAI</t>
+          <t>Convex Finance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1544,7 +1598,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1558,10 +1612,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>69.3</v>
+        <v>76.05</v>
       </c>
       <c r="I8" t="n">
-        <v>69.3</v>
+        <v>76.05</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -1581,13 +1635,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07229147812084041</v>
+        <v>1.938562082632097</v>
       </c>
       <c r="P8" t="n">
-        <v>0.10938</v>
+        <v>2.301</v>
       </c>
       <c r="Q8" t="n">
-        <v>51.30414101806502</v>
+        <v>18.69622441370569</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1595,51 +1649,47 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0.05829284288665879</v>
+        <v>1.585692452707503</v>
       </c>
       <c r="T8" t="n">
-        <v>19.36415687998785</v>
+        <v>18.20264788453316</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07929079573793123</v>
+        <v>2.114996897594393</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08629011335502204</v>
+        <v>2.29143171255669</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999997</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1371052511311159</v>
+        <v>0.08699434536754154</v>
       </c>
       <c r="Z8" t="n">
-        <v>2123.5501847</v>
+        <v>9434.088390000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>3098.7221371</v>
+        <v>6689.09691</v>
       </c>
       <c r="AB8" t="n">
-        <v>175.638742</v>
+        <v>30.636588</v>
       </c>
       <c r="AC8" t="n">
-        <v>5916.380193</v>
+        <v>2557.789488</v>
       </c>
       <c r="AD8" t="n">
-        <v>32258339.42333416</v>
+        <v>231216327.3509655</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1647,12 +1697,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RSRUSDT</t>
+          <t>HSKUSDT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reserve Rights</t>
+          <t>HashKey Platform Token</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1662,7 +1712,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1676,10 +1726,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>68.88</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>68.88</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1703,13 +1753,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001568437375955765</v>
+        <v>0.1636526104988297</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001637</v>
+        <v>0.1753</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.371396977354891</v>
+        <v>7.11714250427653</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1717,40 +1767,40 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0.001305520963919779</v>
+        <v>0.1424215424015932</v>
       </c>
       <c r="T9" t="n">
-        <v>16.76295248165533</v>
+        <v>12.97325354757376</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001699895581973759</v>
+        <v>0.1742681445474479</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001831353787991752</v>
+        <v>0.1848836785960662</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999993</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.06110601894286073</v>
+        <v>0.1140901312036541</v>
       </c>
       <c r="Z9" t="n">
-        <v>13678.54391096</v>
+        <v>19058.436242</v>
       </c>
       <c r="AA9" t="n">
-        <v>9123.01581008</v>
+        <v>16078.493642</v>
       </c>
       <c r="AB9" t="n">
-        <v>31.569205</v>
+        <v>49.975738</v>
       </c>
       <c r="AC9" t="n">
-        <v>113.325533</v>
+        <v>85.83216299999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>102494879.9077956</v>
+        <v>60416021.22862335</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1765,12 +1815,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BANANAS31USDT</t>
+          <t>KAITOUSDT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Banana For Scale</t>
+          <t>KAITO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1780,29 +1830,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>68</v>
+        <v>72.05</v>
       </c>
       <c r="I10" t="n">
-        <v>68</v>
+        <v>72.05</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>none</t>
@@ -1817,13 +1871,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.006683379132221085</v>
+        <v>0.3427586485994695</v>
       </c>
       <c r="P10" t="n">
-        <v>0.007303</v>
+        <v>0.3764</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.271071646851127</v>
+        <v>9.814880394117221</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1831,40 +1885,40 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>0.005490142690138425</v>
+        <v>0.2890202577110645</v>
       </c>
       <c r="T10" t="n">
-        <v>17.85378950492238</v>
+        <v>15.67820129644665</v>
       </c>
       <c r="U10" t="n">
-        <v>0.007279997353262416</v>
+        <v>0.369627844043672</v>
       </c>
       <c r="V10" t="n">
-        <v>0.007876615574303745</v>
+        <v>0.3964970394878746</v>
       </c>
       <c r="W10" t="n">
         <v>0.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9999999999999992</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.07101302815938977</v>
+        <v>0.0266063589197789</v>
       </c>
       <c r="Z10" t="n">
-        <v>9547.791702025999</v>
+        <v>4879.601115</v>
       </c>
       <c r="AA10" t="n">
-        <v>15381.690602652</v>
+        <v>4274.375409</v>
       </c>
       <c r="AB10" t="n">
-        <v>13.445844</v>
+        <v>44.608434</v>
       </c>
       <c r="AC10" t="n">
-        <v>86.75279</v>
+        <v>947.123307</v>
       </c>
       <c r="AD10" t="n">
-        <v>73087551.94585864</v>
+        <v>91006827.83951561</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1879,12 +1933,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DEXEUSDT</t>
+          <t>PLUMEUSDT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DeXe</t>
+          <t>Plume</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1894,24 +1948,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -1931,13 +1985,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.910857108181459</v>
+        <v>0.01058476417612092</v>
       </c>
       <c r="P11" t="n">
-        <v>4.545</v>
+        <v>0.012914</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.21493381826513</v>
+        <v>22.00555236869424</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1945,40 +1999,40 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>3.552733000695246</v>
+        <v>0.008103568598526879</v>
       </c>
       <c r="T11" t="n">
-        <v>9.157176996751497</v>
+        <v>23.44119846516359</v>
       </c>
       <c r="U11" t="n">
-        <v>4.089919161924565</v>
+        <v>0.01182536196491795</v>
       </c>
       <c r="V11" t="n">
-        <v>4.268981215667672</v>
+        <v>0.01306595975371497</v>
       </c>
       <c r="W11" t="n">
-        <v>0.4999999999999994</v>
+        <v>0.5</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.04391743522177821</v>
+        <v>0.1008494627826761</v>
       </c>
       <c r="Z11" t="n">
-        <v>10116.51902</v>
+        <v>14469.16409967</v>
       </c>
       <c r="AA11" t="n">
-        <v>6817.111000000001</v>
+        <v>13031.3457999</v>
       </c>
       <c r="AB11" t="n">
-        <v>27.938813</v>
+        <v>28.998763</v>
       </c>
       <c r="AC11" t="n">
-        <v>3809.599123</v>
+        <v>81.974524</v>
       </c>
       <c r="AD11" t="n">
-        <v>377254741.9074086</v>
+        <v>66248854.3569533</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1993,12 +2047,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RESOLVUSDT</t>
+          <t>ARIAUSDT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Resolv</t>
+          <t>AriaAI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2008,24 +2062,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>68</v>
+        <v>69.3</v>
       </c>
       <c r="I12" t="n">
-        <v>68</v>
+        <v>69.3</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -2045,13 +2099,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09138471627665971</v>
+        <v>0.07229147812084041</v>
       </c>
       <c r="P12" t="n">
-        <v>0.11007</v>
+        <v>0.10454</v>
       </c>
       <c r="Q12" t="n">
-        <v>20.44683671914254</v>
+        <v>44.60902269179481</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2059,47 +2113,51 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0.07396530259278275</v>
+        <v>0.05829284288665879</v>
       </c>
       <c r="T12" t="n">
-        <v>19.06162692582108</v>
+        <v>19.36415687998785</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1000944231185982</v>
+        <v>0.07929079573793123</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1088041299605367</v>
+        <v>0.08629011335502204</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1816200508536069</v>
+        <v>0.1243959619156894</v>
       </c>
       <c r="Z12" t="n">
-        <v>7742.3544959</v>
+        <v>1788.5474865</v>
       </c>
       <c r="AA12" t="n">
-        <v>11275.5325663</v>
+        <v>2121.8590839</v>
       </c>
       <c r="AB12" t="n">
-        <v>34.31382</v>
+        <v>877.980921</v>
       </c>
       <c r="AC12" t="n">
-        <v>88.071566</v>
+        <v>6822.106595</v>
       </c>
       <c r="AD12" t="n">
-        <v>41228346.43992428</v>
+        <v>31074770.19372074</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>low_liquidity</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2107,12 +2165,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZROUSDT</t>
+          <t>ILVUSDT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LayerZero</t>
+          <t>Illuvium</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2122,7 +2180,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2136,15 +2194,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>62.95</v>
+        <v>69.17</v>
       </c>
       <c r="I13" t="n">
-        <v>62.95</v>
+        <v>69.17</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>none</t>
@@ -2159,54 +2221,54 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.790013793265306</v>
+        <v>3.729854108449789</v>
       </c>
       <c r="P13" t="n">
-        <v>2.04</v>
+        <v>3.809</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.96560225821917</v>
+        <v>2.121956764231347</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>1.422371981301922</v>
+        <v>3.13912712196476</v>
       </c>
       <c r="T13" t="n">
-        <v>20.53849044887746</v>
+        <v>15.83780408855047</v>
       </c>
       <c r="U13" t="n">
-        <v>1.973834699246998</v>
+        <v>4.025217601692303</v>
       </c>
       <c r="V13" t="n">
-        <v>2.15765560522869</v>
+        <v>4.320581094934817</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999996</v>
       </c>
       <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.04895960832314977</v>
+        <v>0.2890553146761299</v>
       </c>
       <c r="Z13" t="n">
-        <v>193847.34043</v>
+        <v>4875.3633704</v>
       </c>
       <c r="AA13" t="n">
-        <v>176752.82668</v>
+        <v>4082.6610963</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.812173</v>
+        <v>72.323937</v>
       </c>
       <c r="AC13" t="n">
-        <v>25.458828</v>
+        <v>240.50926</v>
       </c>
       <c r="AD13" t="n">
-        <v>620807634.1729228</v>
+        <v>25907113.36808909</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2221,12 +2283,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JELLYJELLYUSDT</t>
+          <t>RSRUSDT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jelly-My-Jelly</t>
+          <t>Reserve Rights</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2236,7 +2298,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2250,15 +2312,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>62.77</v>
+        <v>68.88</v>
       </c>
       <c r="I14" t="n">
-        <v>62.77</v>
+        <v>68.88</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>none</t>
@@ -2273,30 +2339,30 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.07275696786473181</v>
+        <v>0.001568437375955765</v>
       </c>
       <c r="P14" t="n">
-        <v>0.070906</v>
+        <v>0.001615</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.544042060924101</v>
+        <v>2.968727011868122</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>early</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0.04991201821478376</v>
+        <v>0.001305520963919779</v>
       </c>
       <c r="T14" t="n">
-        <v>31.39898530738786</v>
+        <v>16.76295248165533</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08417944268970583</v>
+        <v>0.001699895581973759</v>
       </c>
       <c r="V14" t="n">
-        <v>0.09560191751467985</v>
+        <v>0.001831353787991752</v>
       </c>
       <c r="W14" t="n">
         <v>0.5</v>
@@ -2305,33 +2371,29 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6056816025969841</v>
+        <v>0.1243008079552547</v>
       </c>
       <c r="Z14" t="n">
-        <v>5677.46448206</v>
+        <v>12589.69799735</v>
       </c>
       <c r="AA14" t="n">
-        <v>4241.80535087</v>
+        <v>11226.81468263</v>
       </c>
       <c r="AB14" t="n">
-        <v>57.553057</v>
+        <v>32.159718</v>
       </c>
       <c r="AC14" t="n">
-        <v>321.916972</v>
+        <v>109.230979</v>
       </c>
       <c r="AD14" t="n">
-        <v>71270276.19260059</v>
+        <v>101548132.372807</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>overextended</t>
-        </is>
-      </c>
+      <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2339,12 +2401,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XMRUSDT</t>
+          <t>BANANAS31USDT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Banana For Scale</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2354,71 +2416,67 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_too_early</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62.3</v>
+        <v>68</v>
       </c>
       <c r="I15" t="n">
-        <v>62.3</v>
+        <v>68</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N15" t="b">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>345.9665807306657</v>
+        <v>0.006759371597630645</v>
       </c>
       <c r="P15" t="n">
-        <v>348.37</v>
+        <v>0.0066784</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6946969456582908</v>
+        <v>-1.197916055673398</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>early</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>299.4234549833657</v>
+        <v>0.005598451967929676</v>
       </c>
       <c r="T15" t="n">
-        <v>13.45306984535993</v>
+        <v>17.17496386953935</v>
       </c>
       <c r="U15" t="n">
-        <v>369.2381436043157</v>
+        <v>0.007339831412481129</v>
       </c>
       <c r="V15" t="n">
-        <v>392.5097064779657</v>
+        <v>0.007920291227331613</v>
       </c>
       <c r="W15" t="n">
         <v>0.5</v>
@@ -2427,22 +2485,22 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.06894966674328003</v>
+        <v>0.04949418443332134</v>
       </c>
       <c r="Z15" t="n">
-        <v>214057.94618</v>
+        <v>14656.377316195</v>
       </c>
       <c r="AA15" t="n">
-        <v>258791.25511</v>
+        <v>13840.045484469</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.301774</v>
+        <v>16.058383</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.517563</v>
+        <v>89.43459799999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>6435439296.008515</v>
+        <v>66903166.88467667</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2457,12 +2515,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRXUSDT</t>
+          <t>RESOLVUSDT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>Resolv</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2472,24 +2530,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_chased</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>reversal</t>
+          <t>pullback</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>reversal_base_reclaim</t>
+          <t>pullback_to_ema</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>62.27</v>
+        <v>68</v>
       </c>
       <c r="I16" t="n">
-        <v>62.27</v>
+        <v>68</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -2497,66 +2555,66 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>none</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>DIRECT_OK</t>
+          <t>MARGINAL</t>
         </is>
       </c>
       <c r="N16" t="b">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.284693334781343</v>
+        <v>0.09357855279855819</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2851</v>
+        <v>0.11703</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1428432523611356</v>
+        <v>25.06070728826566</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>at_trigger</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0.2748952457319503</v>
+        <v>0.07616767090545885</v>
       </c>
       <c r="T16" t="n">
-        <v>3.441629238323416</v>
+        <v>18.60563277846245</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2895923793060393</v>
+        <v>0.1022839937451079</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2944914238307356</v>
+        <v>0.1109894346916575</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4999999999999972</v>
+        <v>0.5</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.03508156463779846</v>
+        <v>0.1281448891546686</v>
       </c>
       <c r="Z16" t="n">
-        <v>489997.04772</v>
+        <v>23813.9449593</v>
       </c>
       <c r="AA16" t="n">
-        <v>477978.962745</v>
+        <v>16772.7729334</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.407751</v>
+        <v>13.756189</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.902349</v>
+        <v>54.545654</v>
       </c>
       <c r="AD16" t="n">
-        <v>27001506355.75538</v>
+        <v>43711855.90736798</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2571,12 +2629,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COWUSDT</t>
+          <t>FLOWUSDT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CoW Protocol</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2586,7 +2644,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>tradeability_marginal | risk_reward_unattractive | btc_regime_caution | entry_not_confirmed | retest_not_reclaimed | entry_chased</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2600,10 +2658,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>61.69</v>
+        <v>66.47</v>
       </c>
       <c r="I17" t="n">
-        <v>61.69</v>
+        <v>66.47</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2627,13 +2685,13 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.218546029029133</v>
+        <v>0.0398287592357851</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2335</v>
+        <v>0.04871</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.842481209701412</v>
+        <v>22.2985624825474</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2641,51 +2699,47 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0.1778745181282117</v>
+        <v>0.0289570776485793</v>
       </c>
       <c r="T17" t="n">
-        <v>18.610043422706</v>
+        <v>27.29605891774274</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2388817844795937</v>
+        <v>0.045264600029388</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2592175399300543</v>
+        <v>0.0507004408229909</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0.9999999999999997</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.08568980291345575</v>
+        <v>0.1435161455663775</v>
       </c>
       <c r="Z17" t="n">
-        <v>14452.858351</v>
+        <v>5093.19474</v>
       </c>
       <c r="AA17" t="n">
-        <v>9653.195133000001</v>
+        <v>2501.6995842</v>
       </c>
       <c r="AB17" t="n">
-        <v>31.216671</v>
+        <v>86.250696</v>
       </c>
       <c r="AC17" t="n">
-        <v>613.614285</v>
+        <v>3161.612786</v>
       </c>
       <c r="AD17" t="n">
-        <v>130980337.6949912</v>
+        <v>80403855.67077628</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>RISK_OFF</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>low_liquidity</t>
-        </is>
-      </c>
+      <c r="AF17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2693,12 +2747,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PIUSDT</t>
+          <t>DEXEUSDT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pi</t>
+          <t>DeXe</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2708,7 +2762,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2722,10 +2776,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>61.6</v>
+        <v>64.8</v>
       </c>
       <c r="I18" t="n">
-        <v>61.6</v>
+        <v>64.8</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -2745,54 +2799,54 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2102080742752865</v>
+        <v>3.968680240504169</v>
       </c>
       <c r="P18" t="n">
-        <v>0.21597</v>
+        <v>4.589</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.74105823221984</v>
+        <v>15.63037891450352</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>late</t>
+          <t>chased</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0.1882159494858924</v>
+        <v>3.603993565019671</v>
       </c>
       <c r="T18" t="n">
-        <v>10.46207424011384</v>
+        <v>9.18911712166989</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2212041366699835</v>
+        <v>4.151023578246418</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2322001990646806</v>
+        <v>4.333366915988668</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999988</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.06019215186943812</v>
+        <v>0.1090631475624363</v>
       </c>
       <c r="Z18" t="n">
-        <v>11233.4431998</v>
+        <v>5064.70722</v>
       </c>
       <c r="AA18" t="n">
-        <v>11550.4014746</v>
+        <v>3111.14463</v>
       </c>
       <c r="AB18" t="n">
-        <v>38.901113</v>
+        <v>69.901804</v>
       </c>
       <c r="AC18" t="n">
-        <v>105.769759</v>
+        <v>6707.375043</v>
       </c>
       <c r="AD18" t="n">
-        <v>2089760326.697821</v>
+        <v>385051702.4890639</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2807,12 +2861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SIGNUSDT</t>
+          <t>ZROUSDT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sign</t>
+          <t>LayerZero</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2822,24 +2876,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_chased</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>61.6</v>
+        <v>62.95</v>
       </c>
       <c r="I19" t="n">
-        <v>61.6</v>
+        <v>62.95</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2859,13 +2913,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04889831448613509</v>
+        <v>1.790013793265306</v>
       </c>
       <c r="P19" t="n">
-        <v>0.05418</v>
+        <v>2.025</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.80136517867607</v>
+        <v>13.12761988867344</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2873,16 +2927,16 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0.04019182784324442</v>
+        <v>1.422371981301922</v>
       </c>
       <c r="T19" t="n">
-        <v>17.80528988449972</v>
+        <v>20.53849044887746</v>
       </c>
       <c r="U19" t="n">
-        <v>0.05325155780758042</v>
+        <v>1.973834699246998</v>
       </c>
       <c r="V19" t="n">
-        <v>0.05760480112902576</v>
+        <v>2.15765560522869</v>
       </c>
       <c r="W19" t="n">
         <v>0.5</v>
@@ -2891,22 +2945,22 @@
         <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.01843487879067759</v>
+        <v>0.04937052579609429</v>
       </c>
       <c r="Z19" t="n">
-        <v>10387.3358469</v>
+        <v>180600.10098</v>
       </c>
       <c r="AA19" t="n">
-        <v>8351.5139844</v>
+        <v>238660.18778</v>
       </c>
       <c r="AB19" t="n">
-        <v>21.471577</v>
+        <v>12.768068</v>
       </c>
       <c r="AC19" t="n">
-        <v>562.695441</v>
+        <v>29.861457</v>
       </c>
       <c r="AD19" t="n">
-        <v>89362648.5698211</v>
+        <v>613496387.3243587</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2921,12 +2975,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KAITOUSDT</t>
+          <t>TRXUSDT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KAITO</t>
+          <t>TRON</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2936,7 +2990,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed</t>
+          <t>risk_reward_unattractive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2950,81 +3004,77 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>60.05</v>
+        <v>61.77</v>
       </c>
       <c r="I20" t="n">
-        <v>60.05</v>
+        <v>61.77</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>retest_not_reclaimed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MARGINAL</t>
+          <t>DIRECT_OK</t>
         </is>
       </c>
       <c r="N20" t="b">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3427586485994695</v>
+        <v>0.284693334781343</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3781</v>
+        <v>0.2854</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.31085620886216</v>
+        <v>0.2482197973478373</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>chased</t>
+          <t>at_trigger</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>0.2890202577110645</v>
+        <v>0.2748952457319503</v>
       </c>
       <c r="T20" t="n">
-        <v>15.67820129644665</v>
+        <v>3.441629238323416</v>
       </c>
       <c r="U20" t="n">
-        <v>0.369627844043672</v>
+        <v>0.2895923793060393</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3964970394878746</v>
+        <v>0.2944914238307356</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999972</v>
       </c>
       <c r="X20" t="n">
         <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.02645152757571459</v>
+        <v>0.03503240497459765</v>
       </c>
       <c r="Z20" t="n">
-        <v>6203.910533</v>
+        <v>509480.112172</v>
       </c>
       <c r="AA20" t="n">
-        <v>3418.298213</v>
+        <v>596771.294218</v>
       </c>
       <c r="AB20" t="n">
-        <v>50.46426</v>
+        <v>1.75162</v>
       </c>
       <c r="AC20" t="n">
-        <v>638.509324</v>
+        <v>2.766436</v>
       </c>
       <c r="AD20" t="n">
-        <v>91276280.15527701</v>
+        <v>27060228935.85907</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3039,12 +3089,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UAIUSDT</t>
+          <t>CAKEUSDT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UnifAI Network</t>
+          <t>PancakeSwap</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3054,29 +3104,33 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>tradeability_marginal | risk_reward_unattractive</t>
+          <t>tradeability_marginal | risk_reward_unattractive | entry_not_confirmed | retest_not_reclaimed | entry_late</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>pullback</t>
+          <t>reversal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>pullback_to_ema</t>
+          <t>reversal_base_reclaim</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>61.27</v>
       </c>
       <c r="I21" t="n">
-        <v>60</v>
+        <v>61.27</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>retest_not_reclaimed</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>none</t>
@@ -3091,54 +3145,54 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3123580685046287</v>
+        <v>1.339000671893962</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3063</v>
+        <v>1.378</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.939462788213164</v>
+        <v>2.912569718943825</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>early</t>
+          <t>late</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>0.2364864965535781</v>
+        <v>1.192386800259678</v>
       </c>
       <c r="T21" t="n">
-        <v>24.28993504610759</v>
+        <v>10.94949948209548</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3502938544801539</v>
+        <v>1.412307607711104</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3882296404556792</v>
+        <v>1.485614543528246</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5</v>
+        <v>0.4999999999999992</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1632120124041131</v>
+        <v>0.0725426187885464</v>
       </c>
       <c r="Z21" t="n">
-        <v>2279.964807</v>
+        <v>127009.14695</v>
       </c>
       <c r="AA21" t="n">
-        <v>5257.189120999999</v>
+        <v>165782.37234</v>
       </c>
       <c r="AB21" t="n">
-        <v>46.017047</v>
+        <v>3.627131</v>
       </c>
       <c r="AC21" t="n">
-        <v>508.075783</v>
+        <v>8.655277999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>73032192.60705574</v>
+        <v>455141299.9602289</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
